--- a/frotas_veiculos.xlsx
+++ b/frotas_veiculos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,49 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cidade_local</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Hb20 1.0</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Hyundai</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Carro</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Eurider</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>51258</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sinop - Mt</t>
         </is>
       </c>
     </row>

--- a/frotas_veiculos.xlsx
+++ b/frotas_veiculos.xlsx
@@ -461,17 +461,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>cidade_local</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>km_atual</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>cidade_local</t>
         </is>
       </c>
     </row>
